--- a/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView/>
+    <workbookView activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" comment="" localSheetId="0" hidden="1">Sheet1!$A$1:$G$5</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18" count="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21" count="22">
   <si>
     <t>Employee ID</t>
   </si>
@@ -71,6 +72,79 @@
   </si>
   <si>
     <t>Contract</t>
+  </si>
+  <si>
+    <t>https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzIuMi44</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -80,29 +154,76 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
+  <fonts count="12">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="000563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="000563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <charset val="0"/>
     </font>
@@ -130,7 +251,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="23">
+  <cellStyleXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
@@ -151,6 +272,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -160,24 +282,117 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="20" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="20" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="20" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>552227</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name="TextBox 3">
+          <a:hlinkClick xmlns:p7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" p7:id="rId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzIuMi44"/>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="18900000">
+          <a:off x="0" y="1"/>
+          <a:ext cx="2076450" cy="1557338"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:alpha val="10000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Created with a trial version of Syncfusion Excel library or registered the 
+wrong key in your application. Click</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0563C1">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> here</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> to obtain the valid key.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-AU" b="1" i="0" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -304,8 +519,47 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:T6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzIuMi44" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
+  <drawing r:id="rId2"/>
+  <extLst/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFF4500"/>
+  </sheetPr>
+  <dimension ref="A10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="10" spans="1:1" ht="25" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="+KqBjSHB4UnRcKdJaUVBQt1W26UuPgjIwlkbGnDkYKsjcx2GpyzOd/JenLo7FLJvoYZ4jDSM5S3JyIdQQ3Pd6w==" saltValue="HDXLgzsOaB3G0+VEfZJzEQ==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A10" r:id="rId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzIuMi44" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
   <extLst/>

--- a/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
@@ -80,28 +80,34 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-    </font>
-    <font>
+  <fonts count="6">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -130,7 +136,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="23">
+  <cellStyleXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
@@ -154,6 +160,7 @@
   </cellStyleXfs>
   <cellXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -180,127 +187,127 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>43845</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>75000</v>
       </c>
-      <c r="F2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>43546</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>120000</v>
       </c>
-      <c r="F3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="28.5">
-      <c r="A4" s="1">
+    <row r="4" spans="1:7">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>44387</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>45000</v>
       </c>
-      <c r="F4" s="1" t="b">
+      <c r="F4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>43409</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>95000</v>
       </c>
-      <c r="F5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
     </row>

--- a/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" comment="" localSheetId="0" hidden="1">Sheet1!$A$1:$G$5</definedName>

--- a/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
+++ b/src/ExcelsiorSyncfusion.Tests/ColumnWidths.Fluent.verified.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView/>
+    <workbookView activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="DeterministicId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" comment="" localSheetId="0" hidden="1">Sheet1!$A$1:$G$5</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18" count="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21" count="22">
   <si>
     <t>Employee ID</t>
   </si>
@@ -71,6 +72,79 @@
   </si>
   <si>
     <t>Contract</t>
+  </si>
+  <si>
+    <t>https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw==</t>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t/>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t>Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> here</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve"> to obtain the valid key.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -80,7 +154,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -109,6 +183,53 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="000563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="000563C1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <charset val="0"/>
     </font>
@@ -136,7 +257,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="24">
+  <cellStyleXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
@@ -157,6 +278,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFont="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -167,24 +289,117 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="20" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="20" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="20" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>418895</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name="TextBox 3">
+          <a:hlinkClick xmlns:p7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" p7:id="rId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw=="/>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="18900000">
+          <a:off x="0" y="1"/>
+          <a:ext cx="2076450" cy="1557338"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF">
+            <a:alpha val="10000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Created with a trial version of Syncfusion Excel library or registered the 
+wrong key in your application. Click</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="0563C1">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> here</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" b="1" i="0" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000">
+                  <a:alpha val="30000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> to obtain the valid key.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-AU" b="1" i="0" sz="1200">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -311,8 +526,47 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:T6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="DeterministicId2" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw==" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
+  <drawing r:id="DeterministicId1"/>
+  <extLst/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFF4500"/>
+  </sheetPr>
+  <dimension ref="A10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="10" spans="1:1" ht="25" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="x5el+YJLbc670EEPMZ3CheXnHiWrRshcOlhH7a3b4EZbDbHl5TfSPoFH4YBq3chXr5yeXgbQgkk68/5zjACl7g==" saltValue="N+N+RwuUtDljuudRGBDldA==" spinCount="500" sheet="1" objects="1" scenarios="1" pivotTables="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A10:S10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A10" r:id="DeterministicId1" tooltip="https://www.syncfusion.com/account/claim-license-key?pl=ZXhjZWw=&amp;vs=MzMuMS40Nw==" display="Created with a trial version of Syncfusion Excel library or registered the wrong key in your application. Click here to obtain the valid key."/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0"/>
   <extLst/>
